--- a/Tests/Validation/Wheat/data/2020Results.xlsx
+++ b/Tests/Validation/Wheat/data/2020Results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,117 +434,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Tips</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Ligules</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.FinalLeafNumber</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Wt</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Live.Wt</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Dead.Wt</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Stem.Wt</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.LAI</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.Zadok.Stage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Ear.Wt</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.Wt</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Number</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Size</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.CoverGreen</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.TerminalSpikeletDAS</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.FloweringDAS</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.MaturityDAS</t>
         </is>
@@ -543,7 +556,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -580,7 +593,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -619,7 +632,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -658,7 +671,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -697,7 +710,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -736,7 +749,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -775,7 +788,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -814,7 +827,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>41610</v>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -865,7 +878,7 @@
           <t>Leeston2013Sow16-AprPopn100</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -924,7 +937,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -961,7 +974,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1000,7 +1013,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1043,7 +1056,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1082,7 +1095,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1123,7 +1136,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1164,7 +1177,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1203,7 +1216,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1244,7 +1257,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1283,7 +1296,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1324,7 +1337,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1363,7 +1376,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1402,7 +1415,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1443,7 +1456,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1482,7 +1495,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1525,7 +1538,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1568,7 +1581,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1611,7 +1624,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>41610</v>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1662,7 +1675,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1699,7 +1712,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1738,7 +1751,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1777,7 +1790,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1814,7 +1827,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>41660</v>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1851,7 +1864,7 @@
           <t>Leeston2013Sow16-AprPopn150</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1910,7 +1923,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1947,7 +1960,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1986,7 +1999,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2025,7 +2038,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2064,7 +2077,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2103,7 +2116,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2142,7 +2155,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2181,7 +2194,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>41610</v>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2232,7 +2245,7 @@
           <t>Leeston2013Sow16-AprPopn200</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2291,7 +2304,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2328,7 +2341,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2367,7 +2380,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2408,7 +2421,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2447,7 +2460,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2486,7 +2499,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2525,7 +2538,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2564,7 +2577,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -2603,7 +2616,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2642,7 +2655,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2681,7 +2694,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -2720,7 +2733,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -2759,7 +2772,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2798,7 +2811,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -2837,7 +2850,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -2878,7 +2891,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2919,7 +2932,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2960,7 +2973,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>41610</v>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3011,7 +3024,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3050,7 +3063,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3091,7 +3104,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -3132,7 +3145,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -3171,7 +3184,7 @@
           <t>Leeston2013Sow16-AprPopn250</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -3230,7 +3243,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -3267,7 +3280,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -3308,7 +3321,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -3353,7 +3366,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -3392,7 +3405,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -3435,7 +3448,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -3478,7 +3491,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -3517,7 +3530,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -3560,7 +3573,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -3599,7 +3612,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -3642,7 +3655,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -3681,7 +3694,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -3720,7 +3733,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -3763,7 +3776,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -3802,7 +3815,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -3847,7 +3860,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -3892,7 +3905,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -3937,7 +3950,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>41610</v>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -3988,7 +4001,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -4027,7 +4040,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -4068,7 +4081,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -4109,7 +4122,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -4148,7 +4161,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>41660</v>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -4185,7 +4198,7 @@
           <t>Leeston2013Sow16-AprPopn50</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -4244,7 +4257,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>41325</v>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -4281,7 +4294,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -4320,7 +4333,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -4359,7 +4372,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -4398,7 +4411,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -4437,7 +4450,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -4476,7 +4489,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -4515,7 +4528,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>41592</v>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -4566,7 +4579,7 @@
           <t>Leeston2013Sow20-FebPopn100</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -4625,7 +4638,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>41325</v>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -4662,7 +4675,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -4703,7 +4716,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -4746,7 +4759,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -4789,7 +4802,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4828,7 +4841,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -4869,7 +4882,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -4910,7 +4923,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -4949,7 +4962,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -4990,7 +5003,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -5029,7 +5042,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -5070,7 +5083,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -5109,7 +5122,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -5148,7 +5161,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -5189,7 +5202,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -5228,7 +5241,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -5271,7 +5284,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -5314,7 +5327,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="3" t="n">
         <v>41592</v>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -5365,7 +5378,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -5408,7 +5421,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -5445,7 +5458,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -5484,7 +5497,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -5523,7 +5536,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -5560,7 +5573,7 @@
           <t>Leeston2013Sow20-FebPopn150</t>
         </is>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -5619,7 +5632,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="3" t="n">
         <v>41325</v>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -5656,7 +5669,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -5695,7 +5708,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -5734,7 +5747,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -5773,7 +5786,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B128" s="1" t="n">
+      <c r="B128" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -5812,7 +5825,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B129" s="1" t="n">
+      <c r="B129" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5851,7 +5864,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B130" s="1" t="n">
+      <c r="B130" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5890,7 +5903,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="3" t="n">
         <v>41592</v>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -5941,7 +5954,7 @@
           <t>Leeston2013Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B132" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -6000,7 +6013,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="3" t="n">
         <v>41325</v>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -6037,7 +6050,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B134" s="1" t="n">
+      <c r="B134" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -6076,7 +6089,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B135" s="1" t="n">
+      <c r="B135" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -6117,7 +6130,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B136" s="1" t="n">
+      <c r="B136" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -6158,7 +6171,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B137" s="1" t="n">
+      <c r="B137" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -6197,7 +6210,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B138" s="1" t="n">
+      <c r="B138" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -6236,7 +6249,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B139" s="1" t="n">
+      <c r="B139" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -6275,7 +6288,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B140" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -6314,7 +6327,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B141" s="1" t="n">
+      <c r="B141" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -6353,7 +6366,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B142" s="1" t="n">
+      <c r="B142" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -6392,7 +6405,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B143" s="1" t="n">
+      <c r="B143" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -6431,7 +6444,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B144" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -6470,7 +6483,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B145" s="1" t="n">
+      <c r="B145" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -6509,7 +6522,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B146" s="1" t="n">
+      <c r="B146" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -6548,7 +6561,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B147" s="1" t="n">
+      <c r="B147" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -6587,7 +6600,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B148" s="1" t="n">
+      <c r="B148" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -6628,7 +6641,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B149" s="1" t="n">
+      <c r="B149" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -6669,7 +6682,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B150" s="1" t="n">
+      <c r="B150" s="3" t="n">
         <v>41592</v>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -6720,7 +6733,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B151" s="1" t="n">
+      <c r="B151" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -6761,7 +6774,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B152" s="1" t="n">
+      <c r="B152" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -6800,7 +6813,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B153" s="1" t="n">
+      <c r="B153" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -6841,7 +6854,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B154" s="1" t="n">
+      <c r="B154" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -6882,7 +6895,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B155" s="1" t="n">
+      <c r="B155" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -6921,7 +6934,7 @@
           <t>Leeston2013Sow20-FebPopn250</t>
         </is>
       </c>
-      <c r="B156" s="1" t="n">
+      <c r="B156" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -6980,7 +6993,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B157" s="1" t="n">
+      <c r="B157" s="3" t="n">
         <v>41325</v>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -7017,7 +7030,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B158" s="1" t="n">
+      <c r="B158" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -7060,7 +7073,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B159" s="1" t="n">
+      <c r="B159" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -7105,7 +7118,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B160" s="1" t="n">
+      <c r="B160" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -7150,7 +7163,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B161" s="1" t="n">
+      <c r="B161" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -7189,7 +7202,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B162" s="1" t="n">
+      <c r="B162" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -7232,7 +7245,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B163" s="1" t="n">
+      <c r="B163" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -7275,7 +7288,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B164" s="1" t="n">
+      <c r="B164" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -7314,7 +7327,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B165" s="1" t="n">
+      <c r="B165" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -7357,7 +7370,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B166" s="1" t="n">
+      <c r="B166" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -7396,7 +7409,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B167" s="1" t="n">
+      <c r="B167" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -7439,7 +7452,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B168" s="1" t="n">
+      <c r="B168" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -7478,7 +7491,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B169" s="1" t="n">
+      <c r="B169" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -7517,7 +7530,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B170" s="1" t="n">
+      <c r="B170" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -7560,7 +7573,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B171" s="1" t="n">
+      <c r="B171" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -7599,7 +7612,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B172" s="1" t="n">
+      <c r="B172" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -7644,7 +7657,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B173" s="1" t="n">
+      <c r="B173" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -7689,7 +7702,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B174" s="1" t="n">
+      <c r="B174" s="3" t="n">
         <v>41592</v>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -7740,7 +7753,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B175" s="1" t="n">
+      <c r="B175" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -7785,7 +7798,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B176" s="1" t="n">
+      <c r="B176" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -7824,7 +7837,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B177" s="1" t="n">
+      <c r="B177" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -7865,7 +7878,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B178" s="1" t="n">
+      <c r="B178" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -7906,7 +7919,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B179" s="1" t="n">
+      <c r="B179" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -7945,7 +7958,7 @@
           <t>Leeston2013Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B180" s="1" t="n">
+      <c r="B180" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -8004,7 +8017,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B181" s="1" t="n">
+      <c r="B181" s="3" t="n">
         <v>41359</v>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -8041,7 +8054,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B182" s="1" t="n">
+      <c r="B182" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -8080,7 +8093,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B183" s="1" t="n">
+      <c r="B183" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -8119,7 +8132,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B184" s="1" t="n">
+      <c r="B184" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -8158,7 +8171,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B185" s="1" t="n">
+      <c r="B185" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -8197,7 +8210,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B186" s="1" t="n">
+      <c r="B186" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -8236,7 +8249,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B187" s="1" t="n">
+      <c r="B187" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -8275,7 +8288,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B188" s="1" t="n">
+      <c r="B188" s="3" t="n">
         <v>41600</v>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -8326,7 +8339,7 @@
           <t>Leeston2013Sow26-MarPopn100</t>
         </is>
       </c>
-      <c r="B189" s="1" t="n">
+      <c r="B189" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -8385,7 +8398,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B190" s="1" t="n">
+      <c r="B190" s="3" t="n">
         <v>41359</v>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -8422,7 +8435,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B191" s="1" t="n">
+      <c r="B191" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -8463,7 +8476,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B192" s="1" t="n">
+      <c r="B192" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -8506,7 +8519,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B193" s="1" t="n">
+      <c r="B193" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -8549,7 +8562,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B194" s="1" t="n">
+      <c r="B194" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -8588,7 +8601,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B195" s="1" t="n">
+      <c r="B195" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -8629,7 +8642,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B196" s="1" t="n">
+      <c r="B196" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -8670,7 +8683,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B197" s="1" t="n">
+      <c r="B197" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -8709,7 +8722,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B198" s="1" t="n">
+      <c r="B198" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -8750,7 +8763,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B199" s="1" t="n">
+      <c r="B199" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -8789,7 +8802,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B200" s="1" t="n">
+      <c r="B200" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -8830,7 +8843,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B201" s="1" t="n">
+      <c r="B201" s="3" t="n">
         <v>41506</v>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -8867,7 +8880,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B202" s="1" t="n">
+      <c r="B202" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -8906,7 +8919,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B203" s="1" t="n">
+      <c r="B203" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -8945,7 +8958,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B204" s="1" t="n">
+      <c r="B204" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -8986,7 +8999,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B205" s="1" t="n">
+      <c r="B205" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -9025,7 +9038,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B206" s="1" t="n">
+      <c r="B206" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -9068,7 +9081,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B207" s="1" t="n">
+      <c r="B207" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -9111,7 +9124,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B208" s="1" t="n">
+      <c r="B208" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -9154,7 +9167,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B209" s="1" t="n">
+      <c r="B209" s="3" t="n">
         <v>41600</v>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -9205,7 +9218,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B210" s="1" t="n">
+      <c r="B210" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -9242,7 +9255,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B211" s="1" t="n">
+      <c r="B211" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -9281,7 +9294,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B212" s="1" t="n">
+      <c r="B212" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -9320,7 +9333,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B213" s="1" t="n">
+      <c r="B213" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -9357,7 +9370,7 @@
           <t>Leeston2013Sow26-MarPopn150</t>
         </is>
       </c>
-      <c r="B214" s="1" t="n">
+      <c r="B214" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C214" t="inlineStr">
@@ -9416,7 +9429,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B215" s="1" t="n">
+      <c r="B215" s="3" t="n">
         <v>41359</v>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -9453,7 +9466,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B216" s="1" t="n">
+      <c r="B216" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -9492,7 +9505,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B217" s="1" t="n">
+      <c r="B217" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -9531,7 +9544,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B218" s="1" t="n">
+      <c r="B218" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -9570,7 +9583,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B219" s="1" t="n">
+      <c r="B219" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -9609,7 +9622,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B220" s="1" t="n">
+      <c r="B220" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -9648,7 +9661,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B221" s="1" t="n">
+      <c r="B221" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -9687,7 +9700,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B222" s="1" t="n">
+      <c r="B222" s="3" t="n">
         <v>41600</v>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -9738,7 +9751,7 @@
           <t>Leeston2013Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B223" s="1" t="n">
+      <c r="B223" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C223" t="inlineStr">
@@ -9797,7 +9810,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B224" s="1" t="n">
+      <c r="B224" s="3" t="n">
         <v>41359</v>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -9834,7 +9847,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B225" s="1" t="n">
+      <c r="B225" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -9873,7 +9886,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B226" s="1" t="n">
+      <c r="B226" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -9914,7 +9927,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B227" s="1" t="n">
+      <c r="B227" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -9955,7 +9968,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B228" s="1" t="n">
+      <c r="B228" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -9994,7 +10007,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B229" s="1" t="n">
+      <c r="B229" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -10033,7 +10046,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B230" s="1" t="n">
+      <c r="B230" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -10072,7 +10085,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B231" s="1" t="n">
+      <c r="B231" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -10111,7 +10124,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B232" s="1" t="n">
+      <c r="B232" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -10150,7 +10163,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B233" s="1" t="n">
+      <c r="B233" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -10189,7 +10202,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B234" s="1" t="n">
+      <c r="B234" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -10228,7 +10241,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B235" s="1" t="n">
+      <c r="B235" s="3" t="n">
         <v>41506</v>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -10265,7 +10278,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B236" s="1" t="n">
+      <c r="B236" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -10304,7 +10317,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B237" s="1" t="n">
+      <c r="B237" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -10343,7 +10356,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B238" s="1" t="n">
+      <c r="B238" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -10382,7 +10395,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B239" s="1" t="n">
+      <c r="B239" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -10421,7 +10434,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B240" s="1" t="n">
+      <c r="B240" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -10462,7 +10475,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B241" s="1" t="n">
+      <c r="B241" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -10503,7 +10516,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B242" s="1" t="n">
+      <c r="B242" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -10544,7 +10557,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B243" s="1" t="n">
+      <c r="B243" s="3" t="n">
         <v>41600</v>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -10595,7 +10608,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B244" s="1" t="n">
+      <c r="B244" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -10634,7 +10647,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B245" s="1" t="n">
+      <c r="B245" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -10675,7 +10688,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B246" s="1" t="n">
+      <c r="B246" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -10716,7 +10729,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B247" s="1" t="n">
+      <c r="B247" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -10755,7 +10768,7 @@
           <t>Leeston2013Sow26-MarPopn250</t>
         </is>
       </c>
-      <c r="B248" s="1" t="n">
+      <c r="B248" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C248" t="inlineStr">
@@ -10814,7 +10827,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B249" s="1" t="n">
+      <c r="B249" s="3" t="n">
         <v>41359</v>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -10851,7 +10864,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B250" s="1" t="n">
+      <c r="B250" s="3" t="n">
         <v>41380</v>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -10894,7 +10907,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B251" s="1" t="n">
+      <c r="B251" s="3" t="n">
         <v>41393</v>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -10939,7 +10952,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B252" s="1" t="n">
+      <c r="B252" s="3" t="n">
         <v>41409</v>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -10984,7 +10997,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B253" s="1" t="n">
+      <c r="B253" s="3" t="n">
         <v>41422</v>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -11023,7 +11036,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B254" s="1" t="n">
+      <c r="B254" s="3" t="n">
         <v>41431</v>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -11066,7 +11079,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B255" s="1" t="n">
+      <c r="B255" s="3" t="n">
         <v>41451</v>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -11109,7 +11122,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B256" s="1" t="n">
+      <c r="B256" s="3" t="n">
         <v>41456</v>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -11148,7 +11161,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B257" s="1" t="n">
+      <c r="B257" s="3" t="n">
         <v>41473</v>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -11191,7 +11204,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B258" s="1" t="n">
+      <c r="B258" s="3" t="n">
         <v>41480</v>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -11230,7 +11243,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B259" s="1" t="n">
+      <c r="B259" s="3" t="n">
         <v>41501</v>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -11273,7 +11286,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B260" s="1" t="n">
+      <c r="B260" s="3" t="n">
         <v>41506</v>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -11310,7 +11323,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B261" s="1" t="n">
+      <c r="B261" s="3" t="n">
         <v>41512</v>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -11349,7 +11362,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B262" s="1" t="n">
+      <c r="B262" s="3" t="n">
         <v>41520</v>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -11388,7 +11401,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B263" s="1" t="n">
+      <c r="B263" s="3" t="n">
         <v>41535</v>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -11431,7 +11444,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B264" s="1" t="n">
+      <c r="B264" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -11470,7 +11483,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B265" s="1" t="n">
+      <c r="B265" s="3" t="n">
         <v>41562</v>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -11515,7 +11528,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B266" s="1" t="n">
+      <c r="B266" s="3" t="n">
         <v>41576</v>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -11560,7 +11573,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B267" s="1" t="n">
+      <c r="B267" s="3" t="n">
         <v>41597</v>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -11605,7 +11618,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B268" s="1" t="n">
+      <c r="B268" s="3" t="n">
         <v>41600</v>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -11656,7 +11669,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B269" s="1" t="n">
+      <c r="B269" s="3" t="n">
         <v>41617</v>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -11695,7 +11708,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B270" s="1" t="n">
+      <c r="B270" s="3" t="n">
         <v>41631</v>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -11736,7 +11749,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B271" s="1" t="n">
+      <c r="B271" s="3" t="n">
         <v>41646</v>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -11777,7 +11790,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B272" s="1" t="n">
+      <c r="B272" s="3" t="n">
         <v>41656</v>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -11816,7 +11829,7 @@
           <t>Leeston2013Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B273" s="1" t="n">
+      <c r="B273" s="3" t="n">
         <v>41667</v>
       </c>
       <c r="C273" t="inlineStr">
@@ -11875,7 +11888,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B274" s="1" t="n">
+      <c r="B274" s="3" t="n">
         <v>41708</v>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -11912,7 +11925,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B275" s="1" t="n">
+      <c r="B275" s="3" t="n">
         <v>41722</v>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -11955,7 +11968,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B276" s="1" t="n">
+      <c r="B276" s="3" t="n">
         <v>41731</v>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -12000,7 +12013,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B277" s="1" t="n">
+      <c r="B277" s="3" t="n">
         <v>41738</v>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -12045,7 +12058,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B278" s="1" t="n">
+      <c r="B278" s="3" t="n">
         <v>41745</v>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -12088,7 +12101,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B279" s="1" t="n">
+      <c r="B279" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -12133,7 +12146,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B280" s="1" t="n">
+      <c r="B280" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -12178,7 +12191,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B281" s="1" t="n">
+      <c r="B281" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -12221,7 +12234,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B282" s="1" t="n">
+      <c r="B282" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -12264,7 +12277,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B283" s="1" t="n">
+      <c r="B283" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -12303,7 +12316,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B284" s="1" t="n">
+      <c r="B284" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -12348,7 +12361,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B285" s="1" t="n">
+      <c r="B285" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -12393,7 +12406,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B286" s="1" t="n">
+      <c r="B286" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -12442,7 +12455,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B287" s="1" t="n">
+      <c r="B287" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -12487,7 +12500,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B288" s="1" t="n">
+      <c r="B288" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -12526,7 +12539,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B289" s="1" t="n">
+      <c r="B289" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -12571,7 +12584,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B290" s="1" t="n">
+      <c r="B290" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -12610,7 +12623,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B291" s="1" t="n">
+      <c r="B291" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -12655,7 +12668,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B292" s="1" t="n">
+      <c r="B292" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -12700,7 +12713,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B293" s="1" t="n">
+      <c r="B293" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -12753,7 +12766,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B294" s="1" t="n">
+      <c r="B294" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -12798,7 +12811,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B295" s="1" t="n">
+      <c r="B295" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -12837,7 +12850,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B296" s="1" t="n">
+      <c r="B296" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -12882,7 +12895,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B297" s="1" t="n">
+      <c r="B297" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -12927,7 +12940,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B298" s="1" t="n">
+      <c r="B298" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -12972,7 +12985,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B299" s="1" t="n">
+      <c r="B299" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -13015,7 +13028,7 @@
           <t>Leeston2014Sow10-MarPopn200</t>
         </is>
       </c>
-      <c r="B300" s="1" t="n">
+      <c r="B300" s="3" t="n">
         <v>42027</v>
       </c>
       <c r="C300" t="inlineStr">
@@ -13074,7 +13087,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B301" s="1" t="n">
+      <c r="B301" s="3" t="n">
         <v>41708</v>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -13111,7 +13124,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B302" s="1" t="n">
+      <c r="B302" s="3" t="n">
         <v>41722</v>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -13154,7 +13167,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B303" s="1" t="n">
+      <c r="B303" s="3" t="n">
         <v>41731</v>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -13199,7 +13212,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B304" s="1" t="n">
+      <c r="B304" s="3" t="n">
         <v>41738</v>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -13244,7 +13257,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B305" s="1" t="n">
+      <c r="B305" s="3" t="n">
         <v>41745</v>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -13287,7 +13300,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B306" s="1" t="n">
+      <c r="B306" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -13332,7 +13345,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B307" s="1" t="n">
+      <c r="B307" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -13377,7 +13390,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B308" s="1" t="n">
+      <c r="B308" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -13420,7 +13433,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B309" s="1" t="n">
+      <c r="B309" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -13463,7 +13476,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B310" s="1" t="n">
+      <c r="B310" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -13502,7 +13515,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B311" s="1" t="n">
+      <c r="B311" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -13547,7 +13560,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B312" s="1" t="n">
+      <c r="B312" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -13592,7 +13605,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B313" s="1" t="n">
+      <c r="B313" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -13641,7 +13654,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B314" s="1" t="n">
+      <c r="B314" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -13686,7 +13699,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B315" s="1" t="n">
+      <c r="B315" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -13725,7 +13738,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B316" s="1" t="n">
+      <c r="B316" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -13770,7 +13783,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B317" s="1" t="n">
+      <c r="B317" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -13809,7 +13822,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B318" s="1" t="n">
+      <c r="B318" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -13854,7 +13867,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B319" s="1" t="n">
+      <c r="B319" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -13899,7 +13912,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B320" s="1" t="n">
+      <c r="B320" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -13952,7 +13965,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B321" s="1" t="n">
+      <c r="B321" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -13997,7 +14010,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B322" s="1" t="n">
+      <c r="B322" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -14036,7 +14049,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B323" s="1" t="n">
+      <c r="B323" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -14081,7 +14094,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B324" s="1" t="n">
+      <c r="B324" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -14126,7 +14139,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B325" s="1" t="n">
+      <c r="B325" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -14171,7 +14184,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B326" s="1" t="n">
+      <c r="B326" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -14216,7 +14229,7 @@
           <t>Leeston2014Sow10-MarPopn50</t>
         </is>
       </c>
-      <c r="B327" s="1" t="n">
+      <c r="B327" s="3" t="n">
         <v>42027</v>
       </c>
       <c r="C327" t="inlineStr">
@@ -14275,7 +14288,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B328" s="1" t="n">
+      <c r="B328" s="3" t="n">
         <v>41690</v>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -14312,7 +14325,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B329" s="1" t="n">
+      <c r="B329" s="3" t="n">
         <v>41709</v>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -14355,7 +14368,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B330" s="1" t="n">
+      <c r="B330" s="3" t="n">
         <v>41710</v>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -14394,7 +14407,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B331" s="1" t="n">
+      <c r="B331" s="3" t="n">
         <v>41722</v>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -14439,7 +14452,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B332" s="1" t="n">
+      <c r="B332" s="3" t="n">
         <v>41731</v>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -14484,7 +14497,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B333" s="1" t="n">
+      <c r="B333" s="3" t="n">
         <v>41738</v>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -14529,7 +14542,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B334" s="1" t="n">
+      <c r="B334" s="3" t="n">
         <v>41745</v>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -14572,7 +14585,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B335" s="1" t="n">
+      <c r="B335" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -14617,7 +14630,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B336" s="1" t="n">
+      <c r="B336" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -14662,7 +14675,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B337" s="1" t="n">
+      <c r="B337" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -14705,7 +14718,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B338" s="1" t="n">
+      <c r="B338" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -14748,7 +14761,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B339" s="1" t="n">
+      <c r="B339" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -14787,7 +14800,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B340" s="1" t="n">
+      <c r="B340" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -14832,7 +14845,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B341" s="1" t="n">
+      <c r="B341" s="3" t="n">
         <v>41844</v>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -14879,7 +14892,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B342" s="1" t="n">
+      <c r="B342" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -14924,7 +14937,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B343" s="1" t="n">
+      <c r="B343" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -14963,7 +14976,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B344" s="1" t="n">
+      <c r="B344" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -15008,7 +15021,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B345" s="1" t="n">
+      <c r="B345" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -15047,7 +15060,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B346" s="1" t="n">
+      <c r="B346" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -15092,7 +15105,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B347" s="1" t="n">
+      <c r="B347" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -15131,7 +15144,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B348" s="1" t="n">
+      <c r="B348" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -15176,7 +15189,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B349" s="1" t="n">
+      <c r="B349" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -15221,7 +15234,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B350" s="1" t="n">
+      <c r="B350" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -15274,7 +15287,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B351" s="1" t="n">
+      <c r="B351" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -15319,7 +15332,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B352" s="1" t="n">
+      <c r="B352" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -15358,7 +15371,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B353" s="1" t="n">
+      <c r="B353" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -15401,7 +15414,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B354" s="1" t="n">
+      <c r="B354" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -15444,7 +15457,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B355" s="1" t="n">
+      <c r="B355" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -15487,7 +15500,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B356" s="1" t="n">
+      <c r="B356" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -15530,7 +15543,7 @@
           <t>Leeston2014Sow20-FebPopn200</t>
         </is>
       </c>
-      <c r="B357" s="1" t="n">
+      <c r="B357" s="3" t="n">
         <v>42027</v>
       </c>
       <c r="C357" t="inlineStr">
@@ -15589,7 +15602,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B358" s="1" t="n">
+      <c r="B358" s="3" t="n">
         <v>41690</v>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -15626,7 +15639,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B359" s="1" t="n">
+      <c r="B359" s="3" t="n">
         <v>41709</v>
       </c>
       <c r="C359" t="inlineStr"/>
@@ -15669,7 +15682,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B360" s="1" t="n">
+      <c r="B360" s="3" t="n">
         <v>41710</v>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -15706,7 +15719,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B361" s="1" t="n">
+      <c r="B361" s="3" t="n">
         <v>41722</v>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -15751,7 +15764,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B362" s="1" t="n">
+      <c r="B362" s="3" t="n">
         <v>41731</v>
       </c>
       <c r="C362" t="inlineStr"/>
@@ -15796,7 +15809,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B363" s="1" t="n">
+      <c r="B363" s="3" t="n">
         <v>41738</v>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -15841,7 +15854,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B364" s="1" t="n">
+      <c r="B364" s="3" t="n">
         <v>41745</v>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -15884,7 +15897,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B365" s="1" t="n">
+      <c r="B365" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -15929,7 +15942,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B366" s="1" t="n">
+      <c r="B366" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -15974,7 +15987,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B367" s="1" t="n">
+      <c r="B367" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -16017,7 +16030,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B368" s="1" t="n">
+      <c r="B368" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -16060,7 +16073,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B369" s="1" t="n">
+      <c r="B369" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -16099,7 +16112,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B370" s="1" t="n">
+      <c r="B370" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -16144,7 +16157,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B371" s="1" t="n">
+      <c r="B371" s="3" t="n">
         <v>41844</v>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -16191,7 +16204,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B372" s="1" t="n">
+      <c r="B372" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -16236,7 +16249,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B373" s="1" t="n">
+      <c r="B373" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -16275,7 +16288,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B374" s="1" t="n">
+      <c r="B374" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -16320,7 +16333,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B375" s="1" t="n">
+      <c r="B375" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -16359,7 +16372,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B376" s="1" t="n">
+      <c r="B376" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -16404,7 +16417,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B377" s="1" t="n">
+      <c r="B377" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -16443,7 +16456,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B378" s="1" t="n">
+      <c r="B378" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -16488,7 +16501,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B379" s="1" t="n">
+      <c r="B379" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -16533,7 +16546,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B380" s="1" t="n">
+      <c r="B380" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -16586,7 +16599,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B381" s="1" t="n">
+      <c r="B381" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C381" t="inlineStr"/>
@@ -16631,7 +16644,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B382" s="1" t="n">
+      <c r="B382" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -16670,7 +16683,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B383" s="1" t="n">
+      <c r="B383" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -16713,7 +16726,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B384" s="1" t="n">
+      <c r="B384" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C384" t="inlineStr"/>
@@ -16756,7 +16769,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B385" s="1" t="n">
+      <c r="B385" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -16799,7 +16812,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B386" s="1" t="n">
+      <c r="B386" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -16842,7 +16855,7 @@
           <t>Leeston2014Sow20-FebPopn50</t>
         </is>
       </c>
-      <c r="B387" s="1" t="n">
+      <c r="B387" s="3" t="n">
         <v>42027</v>
       </c>
       <c r="C387" t="inlineStr">
@@ -16901,7 +16914,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B388" s="1" t="n">
+      <c r="B388" s="3" t="n">
         <v>41752</v>
       </c>
       <c r="C388" t="inlineStr"/>
@@ -16938,7 +16951,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B389" s="1" t="n">
+      <c r="B389" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C389" t="inlineStr"/>
@@ -16977,7 +16990,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B390" s="1" t="n">
+      <c r="B390" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C390" t="inlineStr"/>
@@ -17016,7 +17029,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B391" s="1" t="n">
+      <c r="B391" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C391" t="inlineStr"/>
@@ -17059,7 +17072,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B392" s="1" t="n">
+      <c r="B392" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C392" t="inlineStr"/>
@@ -17102,7 +17115,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B393" s="1" t="n">
+      <c r="B393" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C393" t="inlineStr"/>
@@ -17141,7 +17154,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B394" s="1" t="n">
+      <c r="B394" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C394" t="inlineStr"/>
@@ -17186,7 +17199,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B395" s="1" t="n">
+      <c r="B395" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C395" t="inlineStr"/>
@@ -17231,7 +17244,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B396" s="1" t="n">
+      <c r="B396" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C396" t="inlineStr"/>
@@ -17270,7 +17283,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B397" s="1" t="n">
+      <c r="B397" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C397" t="inlineStr"/>
@@ -17315,7 +17328,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B398" s="1" t="n">
+      <c r="B398" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C398" t="inlineStr"/>
@@ -17354,7 +17367,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B399" s="1" t="n">
+      <c r="B399" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C399" t="inlineStr"/>
@@ -17399,7 +17412,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B400" s="1" t="n">
+      <c r="B400" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -17448,7 +17461,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B401" s="1" t="n">
+      <c r="B401" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -17493,7 +17506,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B402" s="1" t="n">
+      <c r="B402" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C402" t="inlineStr"/>
@@ -17538,7 +17551,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B403" s="1" t="n">
+      <c r="B403" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -17577,7 +17590,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B404" s="1" t="n">
+      <c r="B404" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -17622,7 +17635,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B405" s="1" t="n">
+      <c r="B405" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -17675,7 +17688,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B406" s="1" t="n">
+      <c r="B406" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -17720,7 +17733,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B407" s="1" t="n">
+      <c r="B407" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -17765,7 +17778,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B408" s="1" t="n">
+      <c r="B408" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C408" t="inlineStr"/>
@@ -17810,7 +17823,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B409" s="1" t="n">
+      <c r="B409" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C409" t="inlineStr"/>
@@ -17855,7 +17868,7 @@
           <t>Leeston2014Sow23-AprPopn200</t>
         </is>
       </c>
-      <c r="B410" s="1" t="n">
+      <c r="B410" s="3" t="n">
         <v>42037</v>
       </c>
       <c r="C410" t="inlineStr">
@@ -17914,7 +17927,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B411" s="1" t="n">
+      <c r="B411" s="3" t="n">
         <v>41752</v>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -17951,7 +17964,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B412" s="1" t="n">
+      <c r="B412" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C412" t="inlineStr"/>
@@ -17990,7 +18003,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B413" s="1" t="n">
+      <c r="B413" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C413" t="inlineStr"/>
@@ -18029,7 +18042,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B414" s="1" t="n">
+      <c r="B414" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -18072,7 +18085,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B415" s="1" t="n">
+      <c r="B415" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -18115,7 +18128,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B416" s="1" t="n">
+      <c r="B416" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -18154,7 +18167,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B417" s="1" t="n">
+      <c r="B417" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -18199,7 +18212,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B418" s="1" t="n">
+      <c r="B418" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -18244,7 +18257,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B419" s="1" t="n">
+      <c r="B419" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -18283,7 +18296,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B420" s="1" t="n">
+      <c r="B420" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -18328,7 +18341,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B421" s="1" t="n">
+      <c r="B421" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -18367,7 +18380,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B422" s="1" t="n">
+      <c r="B422" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -18412,7 +18425,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B423" s="1" t="n">
+      <c r="B423" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C423" t="inlineStr"/>
@@ -18461,7 +18474,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B424" s="1" t="n">
+      <c r="B424" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C424" t="inlineStr"/>
@@ -18506,7 +18519,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B425" s="1" t="n">
+      <c r="B425" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C425" t="inlineStr"/>
@@ -18551,7 +18564,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B426" s="1" t="n">
+      <c r="B426" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C426" t="inlineStr"/>
@@ -18590,7 +18603,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B427" s="1" t="n">
+      <c r="B427" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C427" t="inlineStr"/>
@@ -18635,7 +18648,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B428" s="1" t="n">
+      <c r="B428" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -18688,7 +18701,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B429" s="1" t="n">
+      <c r="B429" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C429" t="inlineStr"/>
@@ -18733,7 +18746,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B430" s="1" t="n">
+      <c r="B430" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C430" t="inlineStr"/>
@@ -18778,7 +18791,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B431" s="1" t="n">
+      <c r="B431" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C431" t="inlineStr"/>
@@ -18823,7 +18836,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B432" s="1" t="n">
+      <c r="B432" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C432" t="inlineStr"/>
@@ -18868,7 +18881,7 @@
           <t>Leeston2014Sow23-AprPopn50</t>
         </is>
       </c>
-      <c r="B433" s="1" t="n">
+      <c r="B433" s="3" t="n">
         <v>42037</v>
       </c>
       <c r="C433" t="inlineStr">
@@ -18927,7 +18940,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B434" s="1" t="n">
+      <c r="B434" s="3" t="n">
         <v>41724</v>
       </c>
       <c r="C434" t="inlineStr"/>
@@ -18964,7 +18977,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B435" s="1" t="n">
+      <c r="B435" s="3" t="n">
         <v>41738</v>
       </c>
       <c r="C435" t="inlineStr"/>
@@ -19007,7 +19020,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B436" s="1" t="n">
+      <c r="B436" s="3" t="n">
         <v>41745</v>
       </c>
       <c r="C436" t="inlineStr"/>
@@ -19050,7 +19063,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B437" s="1" t="n">
+      <c r="B437" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C437" t="inlineStr"/>
@@ -19095,7 +19108,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B438" s="1" t="n">
+      <c r="B438" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C438" t="inlineStr"/>
@@ -19140,7 +19153,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B439" s="1" t="n">
+      <c r="B439" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C439" t="inlineStr"/>
@@ -19183,7 +19196,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B440" s="1" t="n">
+      <c r="B440" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -19226,7 +19239,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B441" s="1" t="n">
+      <c r="B441" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -19265,7 +19278,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B442" s="1" t="n">
+      <c r="B442" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -19310,7 +19323,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B443" s="1" t="n">
+      <c r="B443" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -19355,7 +19368,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B444" s="1" t="n">
+      <c r="B444" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -19394,7 +19407,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B445" s="1" t="n">
+      <c r="B445" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -19439,7 +19452,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B446" s="1" t="n">
+      <c r="B446" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C446" t="inlineStr"/>
@@ -19488,7 +19501,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B447" s="1" t="n">
+      <c r="B447" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -19533,7 +19546,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B448" s="1" t="n">
+      <c r="B448" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -19572,7 +19585,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B449" s="1" t="n">
+      <c r="B449" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -19617,7 +19630,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B450" s="1" t="n">
+      <c r="B450" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -19662,7 +19675,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B451" s="1" t="n">
+      <c r="B451" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -19701,7 +19714,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B452" s="1" t="n">
+      <c r="B452" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C452" t="inlineStr"/>
@@ -19746,7 +19759,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B453" s="1" t="n">
+      <c r="B453" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -19799,7 +19812,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B454" s="1" t="n">
+      <c r="B454" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -19844,7 +19857,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B455" s="1" t="n">
+      <c r="B455" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C455" t="inlineStr"/>
@@ -19889,7 +19902,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B456" s="1" t="n">
+      <c r="B456" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -19934,7 +19947,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B457" s="1" t="n">
+      <c r="B457" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C457" t="inlineStr"/>
@@ -19979,7 +19992,7 @@
           <t>Leeston2014Sow26-MarPopn200</t>
         </is>
       </c>
-      <c r="B458" s="1" t="n">
+      <c r="B458" s="3" t="n">
         <v>42027</v>
       </c>
       <c r="C458" t="inlineStr">
@@ -20038,7 +20051,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B459" s="1" t="n">
+      <c r="B459" s="3" t="n">
         <v>41724</v>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -20075,7 +20088,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B460" s="1" t="n">
+      <c r="B460" s="3" t="n">
         <v>41738</v>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -20118,7 +20131,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B461" s="1" t="n">
+      <c r="B461" s="3" t="n">
         <v>41745</v>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -20161,7 +20174,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B462" s="1" t="n">
+      <c r="B462" s="3" t="n">
         <v>41760</v>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -20206,7 +20219,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B463" s="1" t="n">
+      <c r="B463" s="3" t="n">
         <v>41768</v>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -20251,7 +20264,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B464" s="1" t="n">
+      <c r="B464" s="3" t="n">
         <v>41788</v>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -20294,7 +20307,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B465" s="1" t="n">
+      <c r="B465" s="3" t="n">
         <v>41806</v>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -20337,7 +20350,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B466" s="1" t="n">
+      <c r="B466" s="3" t="n">
         <v>41808</v>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -20376,7 +20389,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B467" s="1" t="n">
+      <c r="B467" s="3" t="n">
         <v>41835</v>
       </c>
       <c r="C467" t="inlineStr"/>
@@ -20421,7 +20434,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B468" s="1" t="n">
+      <c r="B468" s="3" t="n">
         <v>41855</v>
       </c>
       <c r="C468" t="inlineStr"/>
@@ -20466,7 +20479,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B469" s="1" t="n">
+      <c r="B469" s="3" t="n">
         <v>41870</v>
       </c>
       <c r="C469" t="inlineStr"/>
@@ -20505,7 +20518,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B470" s="1" t="n">
+      <c r="B470" s="3" t="n">
         <v>41883</v>
       </c>
       <c r="C470" t="inlineStr"/>
@@ -20550,7 +20563,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B471" s="1" t="n">
+      <c r="B471" s="3" t="n">
         <v>41891</v>
       </c>
       <c r="C471" t="inlineStr"/>
@@ -20599,7 +20612,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B472" s="1" t="n">
+      <c r="B472" s="3" t="n">
         <v>41908</v>
       </c>
       <c r="C472" t="inlineStr"/>
@@ -20644,7 +20657,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B473" s="1" t="n">
+      <c r="B473" s="3" t="n">
         <v>41912</v>
       </c>
       <c r="C473" t="inlineStr"/>
@@ -20683,7 +20696,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B474" s="1" t="n">
+      <c r="B474" s="3" t="n">
         <v>41925</v>
       </c>
       <c r="C474" t="inlineStr"/>
@@ -20728,7 +20741,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B475" s="1" t="n">
+      <c r="B475" s="3" t="n">
         <v>41947</v>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -20773,7 +20786,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B476" s="1" t="n">
+      <c r="B476" s="3" t="n">
         <v>41964</v>
       </c>
       <c r="C476" t="inlineStr"/>
@@ -20812,7 +20825,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B477" s="1" t="n">
+      <c r="B477" s="3" t="n">
         <v>41969</v>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -20857,7 +20870,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B478" s="1" t="n">
+      <c r="B478" s="3" t="n">
         <v>41971</v>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -20910,7 +20923,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B479" s="1" t="n">
+      <c r="B479" s="3" t="n">
         <v>41984</v>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -20955,7 +20968,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B480" s="1" t="n">
+      <c r="B480" s="3" t="n">
         <v>41996</v>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -21000,7 +21013,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B481" s="1" t="n">
+      <c r="B481" s="3" t="n">
         <v>42016</v>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -21045,7 +21058,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B482" s="1" t="n">
+      <c r="B482" s="3" t="n">
         <v>42024</v>
       </c>
       <c r="C482" t="inlineStr"/>
@@ -21090,7 +21103,7 @@
           <t>Leeston2014Sow26-MarPopn50</t>
         </is>
       </c>
-      <c r="B483" s="1" t="n">
+      <c r="B483" s="3" t="n">
         <v>42027</v>
       </c>
       <c r="C483" t="inlineStr">
@@ -21149,7 +21162,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B484" s="1" t="n">
+      <c r="B484" s="3" t="n">
         <v>42103</v>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -21186,7 +21199,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B485" s="1" t="n">
+      <c r="B485" s="3" t="n">
         <v>42118</v>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -21225,7 +21238,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B486" s="1" t="n">
+      <c r="B486" s="3" t="n">
         <v>42135</v>
       </c>
       <c r="C486" t="inlineStr"/>
@@ -21268,7 +21281,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B487" s="1" t="n">
+      <c r="B487" s="3" t="n">
         <v>42151</v>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -21311,7 +21324,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B488" s="1" t="n">
+      <c r="B488" s="3" t="n">
         <v>42172</v>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -21354,7 +21367,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B489" s="1" t="n">
+      <c r="B489" s="3" t="n">
         <v>42202</v>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -21397,7 +21410,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B490" s="1" t="n">
+      <c r="B490" s="3" t="n">
         <v>42215</v>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -21436,7 +21449,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B491" s="1" t="n">
+      <c r="B491" s="3" t="n">
         <v>42235</v>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -21479,7 +21492,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B492" s="1" t="n">
+      <c r="B492" s="3" t="n">
         <v>42255</v>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -21522,7 +21535,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B493" s="1" t="n">
+      <c r="B493" s="3" t="n">
         <v>42268</v>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -21561,7 +21574,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B494" s="1" t="n">
+      <c r="B494" s="3" t="n">
         <v>42276</v>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -21612,7 +21625,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B495" s="1" t="n">
+      <c r="B495" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -21655,7 +21668,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B496" s="1" t="n">
+      <c r="B496" s="3" t="n">
         <v>42298</v>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -21698,7 +21711,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B497" s="1" t="n">
+      <c r="B497" s="3" t="n">
         <v>42320</v>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -21741,7 +21754,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B498" s="1" t="n">
+      <c r="B498" s="3" t="n">
         <v>42332</v>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -21780,7 +21793,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B499" s="1" t="n">
+      <c r="B499" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -21819,7 +21832,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B500" s="1" t="n">
+      <c r="B500" s="3" t="n">
         <v>42346</v>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -21876,7 +21889,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B501" s="1" t="n">
+      <c r="B501" s="3" t="n">
         <v>42374</v>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -21917,7 +21930,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B502" s="1" t="n">
+      <c r="B502" s="3" t="n">
         <v>42394</v>
       </c>
       <c r="C502" t="inlineStr"/>
@@ -21958,7 +21971,7 @@
           <t>Wakanui2015Sow09-AprCmNormal</t>
         </is>
       </c>
-      <c r="B503" s="1" t="n">
+      <c r="B503" s="3" t="n">
         <v>42411</v>
       </c>
       <c r="C503" t="inlineStr">
@@ -22017,7 +22030,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B504" s="1" t="n">
+      <c r="B504" s="3" t="n">
         <v>42073</v>
       </c>
       <c r="C504" t="inlineStr"/>
@@ -22054,7 +22067,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B505" s="1" t="n">
+      <c r="B505" s="3" t="n">
         <v>42087</v>
       </c>
       <c r="C505" t="inlineStr"/>
@@ -22097,7 +22110,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B506" s="1" t="n">
+      <c r="B506" s="3" t="n">
         <v>42096</v>
       </c>
       <c r="C506" t="inlineStr"/>
@@ -22140,7 +22153,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B507" s="1" t="n">
+      <c r="B507" s="3" t="n">
         <v>42102</v>
       </c>
       <c r="C507" t="inlineStr"/>
@@ -22183,7 +22196,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B508" s="1" t="n">
+      <c r="B508" s="3" t="n">
         <v>42118</v>
       </c>
       <c r="C508" t="inlineStr"/>
@@ -22226,7 +22239,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B509" s="1" t="n">
+      <c r="B509" s="3" t="n">
         <v>42135</v>
       </c>
       <c r="C509" t="inlineStr"/>
@@ -22269,7 +22282,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B510" s="1" t="n">
+      <c r="B510" s="3" t="n">
         <v>42151</v>
       </c>
       <c r="C510" t="inlineStr"/>
@@ -22312,7 +22325,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B511" s="1" t="n">
+      <c r="B511" s="3" t="n">
         <v>42172</v>
       </c>
       <c r="C511" t="inlineStr"/>
@@ -22355,7 +22368,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B512" s="1" t="n">
+      <c r="B512" s="3" t="n">
         <v>42202</v>
       </c>
       <c r="C512" t="inlineStr"/>
@@ -22398,7 +22411,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B513" s="1" t="n">
+      <c r="B513" s="3" t="n">
         <v>42215</v>
       </c>
       <c r="C513" t="inlineStr"/>
@@ -22437,7 +22450,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B514" s="1" t="n">
+      <c r="B514" s="3" t="n">
         <v>42235</v>
       </c>
       <c r="C514" t="inlineStr"/>
@@ -22480,7 +22493,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B515" s="1" t="n">
+      <c r="B515" s="3" t="n">
         <v>42255</v>
       </c>
       <c r="C515" t="inlineStr"/>
@@ -22535,7 +22548,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B516" s="1" t="n">
+      <c r="B516" s="3" t="n">
         <v>42268</v>
       </c>
       <c r="C516" t="inlineStr"/>
@@ -22574,7 +22587,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B517" s="1" t="n">
+      <c r="B517" s="3" t="n">
         <v>42276</v>
       </c>
       <c r="C517" t="inlineStr"/>
@@ -22613,7 +22626,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B518" s="1" t="n">
+      <c r="B518" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -22656,7 +22669,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B519" s="1" t="n">
+      <c r="B519" s="3" t="n">
         <v>42298</v>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -22699,7 +22712,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B520" s="1" t="n">
+      <c r="B520" s="3" t="n">
         <v>42320</v>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -22742,7 +22755,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B521" s="1" t="n">
+      <c r="B521" s="3" t="n">
         <v>42332</v>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -22781,7 +22794,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B522" s="1" t="n">
+      <c r="B522" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -22834,7 +22847,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B523" s="1" t="n">
+      <c r="B523" s="3" t="n">
         <v>42346</v>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -22877,7 +22890,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B524" s="1" t="n">
+      <c r="B524" s="3" t="n">
         <v>42374</v>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -22918,7 +22931,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B525" s="1" t="n">
+      <c r="B525" s="3" t="n">
         <v>42394</v>
       </c>
       <c r="C525" t="inlineStr"/>
@@ -22959,7 +22972,7 @@
           <t>Wakanui2015Sow10-MarCmNormal</t>
         </is>
       </c>
-      <c r="B526" s="1" t="n">
+      <c r="B526" s="3" t="n">
         <v>42404</v>
       </c>
       <c r="C526" t="inlineStr">
@@ -23018,7 +23031,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B527" s="1" t="n">
+      <c r="B527" s="3" t="n">
         <v>42055</v>
       </c>
       <c r="C527" t="inlineStr"/>
@@ -23055,7 +23068,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B528" s="1" t="n">
+      <c r="B528" s="3" t="n">
         <v>42067</v>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -23094,7 +23107,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B529" s="1" t="n">
+      <c r="B529" s="3" t="n">
         <v>42076</v>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -23137,7 +23150,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B530" s="1" t="n">
+      <c r="B530" s="3" t="n">
         <v>42087</v>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -23180,7 +23193,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B531" s="1" t="n">
+      <c r="B531" s="3" t="n">
         <v>42096</v>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -23223,7 +23236,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B532" s="1" t="n">
+      <c r="B532" s="3" t="n">
         <v>42102</v>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -23266,7 +23279,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B533" s="1" t="n">
+      <c r="B533" s="3" t="n">
         <v>42118</v>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -23309,7 +23322,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B534" s="1" t="n">
+      <c r="B534" s="3" t="n">
         <v>42135</v>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -23352,7 +23365,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B535" s="1" t="n">
+      <c r="B535" s="3" t="n">
         <v>42151</v>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -23395,7 +23408,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B536" s="1" t="n">
+      <c r="B536" s="3" t="n">
         <v>42172</v>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -23438,7 +23451,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B537" s="1" t="n">
+      <c r="B537" s="3" t="n">
         <v>42202</v>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -23481,7 +23494,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B538" s="1" t="n">
+      <c r="B538" s="3" t="n">
         <v>42215</v>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -23532,7 +23545,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B539" s="1" t="n">
+      <c r="B539" s="3" t="n">
         <v>42235</v>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -23575,7 +23588,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B540" s="1" t="n">
+      <c r="B540" s="3" t="n">
         <v>42255</v>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -23618,7 +23631,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B541" s="1" t="n">
+      <c r="B541" s="3" t="n">
         <v>42268</v>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -23657,7 +23670,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B542" s="1" t="n">
+      <c r="B542" s="3" t="n">
         <v>42276</v>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -23696,7 +23709,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B543" s="1" t="n">
+      <c r="B543" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -23739,7 +23752,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B544" s="1" t="n">
+      <c r="B544" s="3" t="n">
         <v>42298</v>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -23782,7 +23795,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B545" s="1" t="n">
+      <c r="B545" s="3" t="n">
         <v>42320</v>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -23825,7 +23838,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B546" s="1" t="n">
+      <c r="B546" s="3" t="n">
         <v>42332</v>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -23878,7 +23891,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B547" s="1" t="n">
+      <c r="B547" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="C547" t="inlineStr"/>
@@ -23917,7 +23930,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B548" s="1" t="n">
+      <c r="B548" s="3" t="n">
         <v>42346</v>
       </c>
       <c r="C548" t="inlineStr"/>
@@ -23960,7 +23973,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B549" s="1" t="n">
+      <c r="B549" s="3" t="n">
         <v>42374</v>
       </c>
       <c r="C549" t="inlineStr"/>
@@ -24001,7 +24014,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B550" s="1" t="n">
+      <c r="B550" s="3" t="n">
         <v>42394</v>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -24042,7 +24055,7 @@
           <t>Wakanui2015Sow20-FebCmNormal</t>
         </is>
       </c>
-      <c r="B551" s="1" t="n">
+      <c r="B551" s="3" t="n">
         <v>42404</v>
       </c>
       <c r="C551" t="inlineStr">
@@ -24101,7 +24114,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B552" s="1" t="n">
+      <c r="B552" s="3" t="n">
         <v>42083</v>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -24138,7 +24151,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B553" s="1" t="n">
+      <c r="B553" s="3" t="n">
         <v>42096</v>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -24179,7 +24192,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B554" s="1" t="n">
+      <c r="B554" s="3" t="n">
         <v>42102</v>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -24222,7 +24235,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B555" s="1" t="n">
+      <c r="B555" s="3" t="n">
         <v>42118</v>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -24265,7 +24278,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B556" s="1" t="n">
+      <c r="B556" s="3" t="n">
         <v>42135</v>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -24308,7 +24321,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B557" s="1" t="n">
+      <c r="B557" s="3" t="n">
         <v>42151</v>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -24351,7 +24364,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B558" s="1" t="n">
+      <c r="B558" s="3" t="n">
         <v>42172</v>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -24394,7 +24407,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B559" s="1" t="n">
+      <c r="B559" s="3" t="n">
         <v>42202</v>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -24437,7 +24450,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B560" s="1" t="n">
+      <c r="B560" s="3" t="n">
         <v>42215</v>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -24476,7 +24489,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B561" s="1" t="n">
+      <c r="B561" s="3" t="n">
         <v>42235</v>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -24519,7 +24532,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B562" s="1" t="n">
+      <c r="B562" s="3" t="n">
         <v>42255</v>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -24562,7 +24575,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B563" s="1" t="n">
+      <c r="B563" s="3" t="n">
         <v>42268</v>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -24613,7 +24626,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B564" s="1" t="n">
+      <c r="B564" s="3" t="n">
         <v>42276</v>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -24652,7 +24665,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B565" s="1" t="n">
+      <c r="B565" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -24695,7 +24708,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B566" s="1" t="n">
+      <c r="B566" s="3" t="n">
         <v>42298</v>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -24738,7 +24751,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B567" s="1" t="n">
+      <c r="B567" s="3" t="n">
         <v>42320</v>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -24781,7 +24794,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B568" s="1" t="n">
+      <c r="B568" s="3" t="n">
         <v>42332</v>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -24820,7 +24833,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B569" s="1" t="n">
+      <c r="B569" s="3" t="n">
         <v>42339</v>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -24873,7 +24886,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B570" s="1" t="n">
+      <c r="B570" s="3" t="n">
         <v>42346</v>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -24916,7 +24929,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B571" s="1" t="n">
+      <c r="B571" s="3" t="n">
         <v>42374</v>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -24957,7 +24970,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B572" s="1" t="n">
+      <c r="B572" s="3" t="n">
         <v>42394</v>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -24998,7 +25011,7 @@
           <t>Wakanui2015Sow20-MarCmNormal</t>
         </is>
       </c>
-      <c r="B573" s="1" t="n">
+      <c r="B573" s="3" t="n">
         <v>42404</v>
       </c>
       <c r="C573" t="inlineStr">
@@ -25057,7 +25070,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B574" s="1" t="n">
+      <c r="B574" s="3" t="n">
         <v>42437</v>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -25094,7 +25107,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B575" s="1" t="n">
+      <c r="B575" s="3" t="n">
         <v>42466</v>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -25137,7 +25150,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B576" s="1" t="n">
+      <c r="B576" s="3" t="n">
         <v>42478</v>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -25180,7 +25193,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B577" s="1" t="n">
+      <c r="B577" s="3" t="n">
         <v>42487</v>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -25219,7 +25232,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B578" s="1" t="n">
+      <c r="B578" s="3" t="n">
         <v>42488</v>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -25258,7 +25271,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B579" s="1" t="n">
+      <c r="B579" s="3" t="n">
         <v>42500</v>
       </c>
       <c r="C579" t="inlineStr"/>
@@ -25297,7 +25310,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B580" s="1" t="n">
+      <c r="B580" s="3" t="n">
         <v>42501</v>
       </c>
       <c r="C580" t="inlineStr"/>
@@ -25340,7 +25353,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B581" s="1" t="n">
+      <c r="B581" s="3" t="n">
         <v>42521</v>
       </c>
       <c r="C581" t="inlineStr"/>
@@ -25381,7 +25394,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B582" s="1" t="n">
+      <c r="B582" s="3" t="n">
         <v>42544</v>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -25424,7 +25437,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B583" s="1" t="n">
+      <c r="B583" s="3" t="n">
         <v>42558</v>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -25463,7 +25476,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B584" s="1" t="n">
+      <c r="B584" s="3" t="n">
         <v>42565</v>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -25506,7 +25519,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B585" s="1" t="n">
+      <c r="B585" s="3" t="n">
         <v>42590</v>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -25549,7 +25562,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B586" s="1" t="n">
+      <c r="B586" s="3" t="n">
         <v>42611</v>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -25588,7 +25601,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B587" s="1" t="n">
+      <c r="B587" s="3" t="n">
         <v>42612</v>
       </c>
       <c r="C587" t="inlineStr"/>
@@ -25631,7 +25644,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B588" s="1" t="n">
+      <c r="B588" s="3" t="n">
         <v>42626</v>
       </c>
       <c r="C588" t="inlineStr"/>
@@ -25682,7 +25695,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B589" s="1" t="n">
+      <c r="B589" s="3" t="n">
         <v>42641</v>
       </c>
       <c r="C589" t="inlineStr"/>
@@ -25725,7 +25738,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B590" s="1" t="n">
+      <c r="B590" s="3" t="n">
         <v>42646</v>
       </c>
       <c r="C590" t="inlineStr"/>
@@ -25764,7 +25777,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B591" s="1" t="n">
+      <c r="B591" s="3" t="n">
         <v>42663</v>
       </c>
       <c r="C591" t="inlineStr"/>
@@ -25805,7 +25818,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B592" s="1" t="n">
+      <c r="B592" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C592" t="inlineStr"/>
@@ -25848,7 +25861,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B593" s="1" t="n">
+      <c r="B593" s="3" t="n">
         <v>42697</v>
       </c>
       <c r="C593" t="inlineStr"/>
@@ -25887,7 +25900,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B594" s="1" t="n">
+      <c r="B594" s="3" t="n">
         <v>42702</v>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -25938,7 +25951,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B595" s="1" t="n">
+      <c r="B595" s="3" t="n">
         <v>42709</v>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -25981,7 +25994,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B596" s="1" t="n">
+      <c r="B596" s="3" t="n">
         <v>42726</v>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -26022,7 +26035,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B597" s="1" t="n">
+      <c r="B597" s="3" t="n">
         <v>42747</v>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -26063,7 +26076,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B598" s="1" t="n">
+      <c r="B598" s="3" t="n">
         <v>42765</v>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -26100,7 +26113,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B599" s="1" t="n">
+      <c r="B599" s="3" t="n">
         <v>42766</v>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -26141,7 +26154,7 @@
           <t>Wakanui2016Sow08-MarCmNormal</t>
         </is>
       </c>
-      <c r="B600" s="1" t="n">
+      <c r="B600" s="3" t="n">
         <v>42776</v>
       </c>
       <c r="C600" t="inlineStr">
@@ -26200,7 +26213,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B601" s="1" t="n">
+      <c r="B601" s="3" t="n">
         <v>42474</v>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -26237,7 +26250,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B602" s="1" t="n">
+      <c r="B602" s="3" t="n">
         <v>42487</v>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -26276,7 +26289,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B603" s="1" t="n">
+      <c r="B603" s="3" t="n">
         <v>42488</v>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -26315,7 +26328,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B604" s="1" t="n">
+      <c r="B604" s="3" t="n">
         <v>42500</v>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -26354,7 +26367,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B605" s="1" t="n">
+      <c r="B605" s="3" t="n">
         <v>42501</v>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -26397,7 +26410,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B606" s="1" t="n">
+      <c r="B606" s="3" t="n">
         <v>42521</v>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -26438,7 +26451,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B607" s="1" t="n">
+      <c r="B607" s="3" t="n">
         <v>42544</v>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -26481,7 +26494,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B608" s="1" t="n">
+      <c r="B608" s="3" t="n">
         <v>42558</v>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -26520,7 +26533,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B609" s="1" t="n">
+      <c r="B609" s="3" t="n">
         <v>42565</v>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -26563,7 +26576,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B610" s="1" t="n">
+      <c r="B610" s="3" t="n">
         <v>42590</v>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -26606,7 +26619,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B611" s="1" t="n">
+      <c r="B611" s="3" t="n">
         <v>42611</v>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -26645,7 +26658,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B612" s="1" t="n">
+      <c r="B612" s="3" t="n">
         <v>42612</v>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -26688,7 +26701,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B613" s="1" t="n">
+      <c r="B613" s="3" t="n">
         <v>42626</v>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -26727,7 +26740,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B614" s="1" t="n">
+      <c r="B614" s="3" t="n">
         <v>42641</v>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -26770,7 +26783,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B615" s="1" t="n">
+      <c r="B615" s="3" t="n">
         <v>42646</v>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -26821,7 +26834,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B616" s="1" t="n">
+      <c r="B616" s="3" t="n">
         <v>42663</v>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -26862,7 +26875,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B617" s="1" t="n">
+      <c r="B617" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -26905,7 +26918,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B618" s="1" t="n">
+      <c r="B618" s="3" t="n">
         <v>42697</v>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -26944,7 +26957,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B619" s="1" t="n">
+      <c r="B619" s="3" t="n">
         <v>42709</v>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -27001,7 +27014,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B620" s="1" t="n">
+      <c r="B620" s="3" t="n">
         <v>42726</v>
       </c>
       <c r="C620" t="inlineStr"/>
@@ -27042,7 +27055,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B621" s="1" t="n">
+      <c r="B621" s="3" t="n">
         <v>42747</v>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -27083,7 +27096,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B622" s="1" t="n">
+      <c r="B622" s="3" t="n">
         <v>42765</v>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -27120,7 +27133,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B623" s="1" t="n">
+      <c r="B623" s="3" t="n">
         <v>42766</v>
       </c>
       <c r="C623" t="inlineStr"/>
@@ -27161,7 +27174,7 @@
           <t>Wakanui2016Sow14-AprCmNormal</t>
         </is>
       </c>
-      <c r="B624" s="1" t="n">
+      <c r="B624" s="3" t="n">
         <v>42776</v>
       </c>
       <c r="C624" t="inlineStr">
@@ -27220,7 +27233,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B625" s="1" t="n">
+      <c r="B625" s="3" t="n">
         <v>42424</v>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -27257,7 +27270,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B626" s="1" t="n">
+      <c r="B626" s="3" t="n">
         <v>42447</v>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -27300,7 +27313,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B627" s="1" t="n">
+      <c r="B627" s="3" t="n">
         <v>42466</v>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -27343,7 +27356,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B628" s="1" t="n">
+      <c r="B628" s="3" t="n">
         <v>42478</v>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -27386,7 +27399,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B629" s="1" t="n">
+      <c r="B629" s="3" t="n">
         <v>42487</v>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -27425,7 +27438,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B630" s="1" t="n">
+      <c r="B630" s="3" t="n">
         <v>42488</v>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -27464,7 +27477,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B631" s="1" t="n">
+      <c r="B631" s="3" t="n">
         <v>42500</v>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -27503,7 +27516,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B632" s="1" t="n">
+      <c r="B632" s="3" t="n">
         <v>42501</v>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -27546,7 +27559,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B633" s="1" t="n">
+      <c r="B633" s="3" t="n">
         <v>42521</v>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -27587,7 +27600,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B634" s="1" t="n">
+      <c r="B634" s="3" t="n">
         <v>42544</v>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -27630,7 +27643,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B635" s="1" t="n">
+      <c r="B635" s="3" t="n">
         <v>42558</v>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -27669,7 +27682,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B636" s="1" t="n">
+      <c r="B636" s="3" t="n">
         <v>42565</v>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -27712,7 +27725,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B637" s="1" t="n">
+      <c r="B637" s="3" t="n">
         <v>42579</v>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -27761,7 +27774,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B638" s="1" t="n">
+      <c r="B638" s="3" t="n">
         <v>42590</v>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -27804,7 +27817,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B639" s="1" t="n">
+      <c r="B639" s="3" t="n">
         <v>42611</v>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -27843,7 +27856,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B640" s="1" t="n">
+      <c r="B640" s="3" t="n">
         <v>42612</v>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -27886,7 +27899,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B641" s="1" t="n">
+      <c r="B641" s="3" t="n">
         <v>42626</v>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -27925,7 +27938,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B642" s="1" t="n">
+      <c r="B642" s="3" t="n">
         <v>42641</v>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -27968,7 +27981,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B643" s="1" t="n">
+      <c r="B643" s="3" t="n">
         <v>42646</v>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -28007,7 +28020,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B644" s="1" t="n">
+      <c r="B644" s="3" t="n">
         <v>42663</v>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -28048,7 +28061,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B645" s="1" t="n">
+      <c r="B645" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -28091,7 +28104,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B646" s="1" t="n">
+      <c r="B646" s="3" t="n">
         <v>42697</v>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -28130,7 +28143,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B647" s="1" t="n">
+      <c r="B647" s="3" t="n">
         <v>42702</v>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -28181,7 +28194,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B648" s="1" t="n">
+      <c r="B648" s="3" t="n">
         <v>42709</v>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -28224,7 +28237,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B649" s="1" t="n">
+      <c r="B649" s="3" t="n">
         <v>42726</v>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -28265,7 +28278,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B650" s="1" t="n">
+      <c r="B650" s="3" t="n">
         <v>42747</v>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -28306,7 +28319,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B651" s="1" t="n">
+      <c r="B651" s="3" t="n">
         <v>42765</v>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -28343,7 +28356,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B652" s="1" t="n">
+      <c r="B652" s="3" t="n">
         <v>42766</v>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -28384,7 +28397,7 @@
           <t>Wakanui2016Sow24-FebCmNormal</t>
         </is>
       </c>
-      <c r="B653" s="1" t="n">
+      <c r="B653" s="3" t="n">
         <v>42776</v>
       </c>
       <c r="C653" t="inlineStr">
@@ -28443,7 +28456,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B654" s="1" t="n">
+      <c r="B654" s="3" t="n">
         <v>42458</v>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -28480,7 +28493,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B655" s="1" t="n">
+      <c r="B655" s="3" t="n">
         <v>42478</v>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -28523,7 +28536,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B656" s="1" t="n">
+      <c r="B656" s="3" t="n">
         <v>42487</v>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -28562,7 +28575,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B657" s="1" t="n">
+      <c r="B657" s="3" t="n">
         <v>42488</v>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -28601,7 +28614,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B658" s="1" t="n">
+      <c r="B658" s="3" t="n">
         <v>42500</v>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -28640,7 +28653,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B659" s="1" t="n">
+      <c r="B659" s="3" t="n">
         <v>42501</v>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -28683,7 +28696,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B660" s="1" t="n">
+      <c r="B660" s="3" t="n">
         <v>42521</v>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -28724,7 +28737,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B661" s="1" t="n">
+      <c r="B661" s="3" t="n">
         <v>42544</v>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -28767,7 +28780,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B662" s="1" t="n">
+      <c r="B662" s="3" t="n">
         <v>42558</v>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -28806,7 +28819,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B663" s="1" t="n">
+      <c r="B663" s="3" t="n">
         <v>42565</v>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -28849,7 +28862,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B664" s="1" t="n">
+      <c r="B664" s="3" t="n">
         <v>42590</v>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -28892,7 +28905,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B665" s="1" t="n">
+      <c r="B665" s="3" t="n">
         <v>42611</v>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -28931,7 +28944,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B666" s="1" t="n">
+      <c r="B666" s="3" t="n">
         <v>42612</v>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -28974,7 +28987,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B667" s="1" t="n">
+      <c r="B667" s="3" t="n">
         <v>42626</v>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -29025,7 +29038,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B668" s="1" t="n">
+      <c r="B668" s="3" t="n">
         <v>42641</v>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -29068,7 +29081,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B669" s="1" t="n">
+      <c r="B669" s="3" t="n">
         <v>42646</v>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -29107,7 +29120,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B670" s="1" t="n">
+      <c r="B670" s="3" t="n">
         <v>42663</v>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -29148,7 +29161,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B671" s="1" t="n">
+      <c r="B671" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -29191,7 +29204,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B672" s="1" t="n">
+      <c r="B672" s="3" t="n">
         <v>42697</v>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -29230,7 +29243,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B673" s="1" t="n">
+      <c r="B673" s="3" t="n">
         <v>42702</v>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -29281,7 +29294,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B674" s="1" t="n">
+      <c r="B674" s="3" t="n">
         <v>42709</v>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -29324,7 +29337,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B675" s="1" t="n">
+      <c r="B675" s="3" t="n">
         <v>42726</v>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -29365,7 +29378,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B676" s="1" t="n">
+      <c r="B676" s="3" t="n">
         <v>42747</v>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -29406,7 +29419,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B677" s="1" t="n">
+      <c r="B677" s="3" t="n">
         <v>42765</v>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -29443,7 +29456,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B678" s="1" t="n">
+      <c r="B678" s="3" t="n">
         <v>42766</v>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -29484,7 +29497,7 @@
           <t>Wakanui2016Sow29-MarCmNormal</t>
         </is>
       </c>
-      <c r="B679" s="1" t="n">
+      <c r="B679" s="3" t="n">
         <v>42776</v>
       </c>
       <c r="C679" t="inlineStr">
@@ -29543,7 +29556,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B680" s="1" t="n">
+      <c r="B680" s="3" t="n">
         <v>42803</v>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -29580,7 +29593,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B681" s="1" t="n">
+      <c r="B681" s="3" t="n">
         <v>42818</v>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -29623,7 +29636,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B682" s="1" t="n">
+      <c r="B682" s="3" t="n">
         <v>42835</v>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -29668,7 +29681,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B683" s="1" t="n">
+      <c r="B683" s="3" t="n">
         <v>42858</v>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -29711,7 +29724,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B684" s="1" t="n">
+      <c r="B684" s="3" t="n">
         <v>42863</v>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -29750,7 +29763,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B685" s="1" t="n">
+      <c r="B685" s="3" t="n">
         <v>42880</v>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -29795,7 +29808,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B686" s="1" t="n">
+      <c r="B686" s="3" t="n">
         <v>42898</v>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -29840,7 +29853,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B687" s="1" t="n">
+      <c r="B687" s="3" t="n">
         <v>42919</v>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -29885,7 +29898,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B688" s="1" t="n">
+      <c r="B688" s="3" t="n">
         <v>42934</v>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -29924,7 +29937,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B689" s="1" t="n">
+      <c r="B689" s="3" t="n">
         <v>42947</v>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -29967,7 +29980,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B690" s="1" t="n">
+      <c r="B690" s="3" t="n">
         <v>42964</v>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -30024,7 +30037,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B691" s="1" t="n">
+      <c r="B691" s="3" t="n">
         <v>42986</v>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -30069,7 +30082,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B692" s="1" t="n">
+      <c r="B692" s="3" t="n">
         <v>43013</v>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -30114,7 +30127,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B693" s="1" t="n">
+      <c r="B693" s="3" t="n">
         <v>43028</v>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -30159,7 +30172,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B694" s="1" t="n">
+      <c r="B694" s="3" t="n">
         <v>43046</v>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -30204,7 +30217,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B695" s="1" t="n">
+      <c r="B695" s="3" t="n">
         <v>43059</v>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -30257,7 +30270,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B696" s="1" t="n">
+      <c r="B696" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -30300,7 +30313,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B697" s="1" t="n">
+      <c r="B697" s="3" t="n">
         <v>43090</v>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -30345,7 +30358,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B698" s="1" t="n">
+      <c r="B698" s="3" t="n">
         <v>43117</v>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -30390,7 +30403,7 @@
           <t>Wakanui2017Sow09-MarCmNormal</t>
         </is>
       </c>
-      <c r="B699" s="1" t="n">
+      <c r="B699" s="3" t="n">
         <v>43123</v>
       </c>
       <c r="C699" t="inlineStr">
@@ -30451,7 +30464,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B700" s="1" t="n">
+      <c r="B700" s="3" t="n">
         <v>42844</v>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -30488,7 +30501,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B701" s="1" t="n">
+      <c r="B701" s="3" t="n">
         <v>42858</v>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -30529,7 +30542,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B702" s="1" t="n">
+      <c r="B702" s="3" t="n">
         <v>42863</v>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -30568,7 +30581,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B703" s="1" t="n">
+      <c r="B703" s="3" t="n">
         <v>42880</v>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -30613,7 +30626,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B704" s="1" t="n">
+      <c r="B704" s="3" t="n">
         <v>42898</v>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -30658,7 +30671,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B705" s="1" t="n">
+      <c r="B705" s="3" t="n">
         <v>42919</v>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -30703,7 +30716,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B706" s="1" t="n">
+      <c r="B706" s="3" t="n">
         <v>42934</v>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -30742,7 +30755,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B707" s="1" t="n">
+      <c r="B707" s="3" t="n">
         <v>42947</v>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -30785,7 +30798,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B708" s="1" t="n">
+      <c r="B708" s="3" t="n">
         <v>42964</v>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -30830,7 +30843,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B709" s="1" t="n">
+      <c r="B709" s="3" t="n">
         <v>42986</v>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -30875,7 +30888,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B710" s="1" t="n">
+      <c r="B710" s="3" t="n">
         <v>43013</v>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -30932,7 +30945,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B711" s="1" t="n">
+      <c r="B711" s="3" t="n">
         <v>43028</v>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -30977,7 +30990,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B712" s="1" t="n">
+      <c r="B712" s="3" t="n">
         <v>43046</v>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -31022,7 +31035,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B713" s="1" t="n">
+      <c r="B713" s="3" t="n">
         <v>43067</v>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -31075,7 +31088,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B714" s="1" t="n">
+      <c r="B714" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="C714" t="inlineStr"/>
@@ -31118,7 +31131,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B715" s="1" t="n">
+      <c r="B715" s="3" t="n">
         <v>43090</v>
       </c>
       <c r="C715" t="inlineStr"/>
@@ -31163,7 +31176,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B716" s="1" t="n">
+      <c r="B716" s="3" t="n">
         <v>43117</v>
       </c>
       <c r="C716" t="inlineStr"/>
@@ -31208,7 +31221,7 @@
           <t>Wakanui2017Sow19-AprCmNormal</t>
         </is>
       </c>
-      <c r="B717" s="1" t="n">
+      <c r="B717" s="3" t="n">
         <v>43129</v>
       </c>
       <c r="C717" t="inlineStr">
@@ -31273,7 +31286,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B718" s="1" t="n">
+      <c r="B718" s="3" t="n">
         <v>42824</v>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -31310,7 +31323,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B719" s="1" t="n">
+      <c r="B719" s="3" t="n">
         <v>42835</v>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -31351,7 +31364,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B720" s="1" t="n">
+      <c r="B720" s="3" t="n">
         <v>42858</v>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -31394,7 +31407,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B721" s="1" t="n">
+      <c r="B721" s="3" t="n">
         <v>42863</v>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -31433,7 +31446,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B722" s="1" t="n">
+      <c r="B722" s="3" t="n">
         <v>42880</v>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -31478,7 +31491,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B723" s="1" t="n">
+      <c r="B723" s="3" t="n">
         <v>42898</v>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -31523,7 +31536,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B724" s="1" t="n">
+      <c r="B724" s="3" t="n">
         <v>42919</v>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -31568,7 +31581,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B725" s="1" t="n">
+      <c r="B725" s="3" t="n">
         <v>42934</v>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -31607,7 +31620,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B726" s="1" t="n">
+      <c r="B726" s="3" t="n">
         <v>42947</v>
       </c>
       <c r="C726" t="inlineStr"/>
@@ -31650,7 +31663,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B727" s="1" t="n">
+      <c r="B727" s="3" t="n">
         <v>42964</v>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -31695,7 +31708,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B728" s="1" t="n">
+      <c r="B728" s="3" t="n">
         <v>42986</v>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -31752,7 +31765,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B729" s="1" t="n">
+      <c r="B729" s="3" t="n">
         <v>43013</v>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -31797,7 +31810,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B730" s="1" t="n">
+      <c r="B730" s="3" t="n">
         <v>43028</v>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -31842,7 +31855,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B731" s="1" t="n">
+      <c r="B731" s="3" t="n">
         <v>43046</v>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -31887,7 +31900,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B732" s="1" t="n">
+      <c r="B732" s="3" t="n">
         <v>43067</v>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -31940,7 +31953,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B733" s="1" t="n">
+      <c r="B733" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -31983,7 +31996,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B734" s="1" t="n">
+      <c r="B734" s="3" t="n">
         <v>43090</v>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -32028,7 +32041,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B735" s="1" t="n">
+      <c r="B735" s="3" t="n">
         <v>43117</v>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -32073,7 +32086,7 @@
           <t>Wakanui2017Sow30-MarCmNormal</t>
         </is>
       </c>
-      <c r="B736" s="1" t="n">
+      <c r="B736" s="3" t="n">
         <v>43129</v>
       </c>
       <c r="C736" t="inlineStr">
